--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124327287</v>
+        <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551461</v>
+        <v>551440</v>
       </c>
       <c r="R2" t="n">
-        <v>6577514</v>
+        <v>6577472</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer i mossrik ängsgranskog.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124327655</v>
+        <v>124327287</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,39 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551440</v>
+        <v>551461</v>
       </c>
       <c r="R3" t="n">
-        <v>6577472</v>
+        <v>6577514</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,7 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer i mossrik ängsgranskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124327655</v>
+        <v>124327287</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551440</v>
+        <v>551461</v>
       </c>
       <c r="R2" t="n">
-        <v>6577472</v>
+        <v>6577514</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer i mossrik ängsgranskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124327287</v>
+        <v>124327655</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +816,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551461</v>
+        <v>551440</v>
       </c>
       <c r="R3" t="n">
-        <v>6577514</v>
+        <v>6577472</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +901,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer i mossrik ängsgranskog.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17706-2025 artfynd.xlsx
+++ b/artfynd/A 17706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124327655</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
+        <v>58037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
